--- a/xlsx/Gérard.xlsx
+++ b/xlsx/Gérard.xlsx
@@ -5833,7 +5833,7 @@
 3. Larghetto (B-flat major) [similaire au 3e mouvement G 482, avec modifications] - [Larghetto / Allegro / Presto / Larghetto]</t>
   </si>
   <si>
-    <t>[premmière version]</t>
+    <t>[1st version]</t>
   </si>
   <si>
     <t>G. 566</t>
